--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:51</t>
+          <t>2026-05-05 20:19</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Unmatched_Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unmatched_Log'!$A$4:$H$19</definedName>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unmatched_Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Unmatched_Log" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unmatched_Log'!$A$4:$H$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Unmatched_Log'!$A$4:$H$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -572,27 +572,27 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>71-0558</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>71-0558 สมัย 6W</t>
+          <t>71-5041 เกรียงไกร หัวลาก10W มะยม</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
-        <v>46132.67310185185</v>
+        <v>46170.79800925926</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>46132.70556712963</v>
+        <v>46170.92944444445</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.7792</v>
+        <v>3.1544</v>
       </c>
       <c r="H5" s="5" t="n"/>
     </row>
@@ -614,17 +614,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E6" s="8" t="n">
-        <v>46133.37346064814</v>
+        <v>46144.28349537037</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>46133.42685185185</v>
+        <v>46144.68111111111</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1.2814</v>
+        <v>9.5428</v>
       </c>
       <c r="H6" s="7" t="n"/>
     </row>
@@ -636,59 +636,59 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>71-6802 วิชาญ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>10.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>46127.49755787037</v>
+        <v>46144.76762731482</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>46127.61575231481</v>
+        <v>46144.91346064815</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.8367</v>
+        <v>3.5</v>
       </c>
       <c r="H7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>71-6802 วิชาญ หัวลาก10W</t>
+          <t>71-5042 ณัชพน หัวลาก10W</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="E8" s="8" t="n">
-        <v>46131.56739583334</v>
+        <v>46161.60991898148</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>46131.61234953703</v>
+        <v>46161.67677083334</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>1.0789</v>
+        <v>1.6044</v>
       </c>
       <c r="H8" s="7" t="n"/>
     </row>
@@ -700,27 +700,27 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>71-8003 เกศศักดิ์ หัวลาก10W</t>
+          <t>71-6802 นิพล หัวลาก10W</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
-        <v>46122.29600694445</v>
+        <v>46145.53759259259</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>46122.29638888889</v>
+        <v>46145.76045138889</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0092</v>
+        <v>5.3486</v>
       </c>
       <c r="H9" s="5" t="n"/>
     </row>
@@ -732,27 +732,27 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>71-8681 ว่าง หัวลาก10W อ้อย</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="E10" s="8" t="n">
-        <v>46142.43232638889</v>
+        <v>46161.39701388889</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>46142.79065972222</v>
+        <v>46161.51679398148</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>8.6</v>
+        <v>2.8747</v>
       </c>
       <c r="H10" s="7" t="n"/>
     </row>
@@ -764,27 +764,27 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>71-8967 ณัฐวุฒิ หัวลาก10W ทับทิม</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
-        <v>46128.36091435186</v>
+        <v>46161.81990740741</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>46128.42667824074</v>
+        <v>46161.82114583333</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.5783</v>
+        <v>0.0297</v>
       </c>
       <c r="H11" s="5" t="n"/>
     </row>
@@ -796,27 +796,27 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>71-8967 ณัฐวุฒิ หัวลาก10W ทับทิม</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="E12" s="8" t="n">
-        <v>46132.57429398148</v>
+        <v>46161.82883101852</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>46132.57704861111</v>
+        <v>46161.83010416666</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.0306</v>
       </c>
       <c r="H12" s="7" t="n"/>
     </row>
@@ -828,187 +828,187 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>71-8967</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>71-8967 ณัฐวุฒิ หัวลาก10W ทับทิม</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>12.9</t>
+          <t>10.4</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
-        <v>46132.61444444444</v>
+        <v>46161.83834490741</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>46141.71886574074</v>
+        <v>46162.6471875</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>218.5061</v>
+        <v>19.4122</v>
       </c>
       <c r="H13" s="5" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>71-9629 พิชิต หัวลาก10W แมงลัก</t>
+          <t>71-8001 มานพ หัวลาก10W</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="E14" s="8" t="n">
-        <v>46131.95385416667</v>
+        <v>46162.65172453703</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>46132.17018518518</v>
+        <v>46162.65283564815</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>5.1919</v>
+        <v>0.0267</v>
       </c>
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>71-9629 พิชิต หัวลาก10W แมงลัก</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
-        <v>46132.86519675926</v>
+        <v>46155.91594907407</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>46132.92870370371</v>
+        <v>46155.93128472222</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.5242</v>
+        <v>0.3681</v>
       </c>
       <c r="H15" s="5" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>71-9629 พิชิต หัวลาก10W แมงลัก</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>8.16</t>
         </is>
       </c>
       <c r="E16" s="8" t="n">
-        <v>46132.93228009259</v>
+        <v>46164.50247685185</v>
       </c>
       <c r="F16" s="8" t="n">
-        <v>46132.94092592593</v>
+        <v>46164.52361111111</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>0.2075</v>
+        <v>0.5072</v>
       </c>
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Origin</t>
+          <t>Destination</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>71-9629 พิชิต หัวลาก10W แมงลัก</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
-        <v>46134.91841435185</v>
+        <v>46166.93170138889</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>46135.06695601852</v>
+        <v>46166.97837962963</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>3.565</v>
+        <v>1.1203</v>
       </c>
       <c r="H17" s="5" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Destination</t>
+          <t>Origin</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>72-1220 ปกรณ์ หัวลาก10W ข่า</t>
+          <t>71-8002 สมประสงค์ หัวลาก10W</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="E18" s="8" t="n">
-        <v>46126.58716435185</v>
+        <v>46173.44228009259</v>
       </c>
       <c r="F18" s="8" t="n">
-        <v>46126.6124537037</v>
+        <v>46173.98832175926</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>0.6069</v>
+        <v>13.105</v>
       </c>
       <c r="H18" s="7" t="n"/>
     </row>
@@ -1020,32 +1020,256 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>72-1220 ปกรณ์ หัวลาก10W ข่า</t>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>10.7</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>46127.57850694445</v>
+        <v>46172.63181712963</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>46127.99334490741</v>
+        <v>46172.65370370371</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>9.956099999999999</v>
+        <v>0.5253</v>
       </c>
       <c r="H19" s="5" t="n"/>
     </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>71-8003 โกสินทร์ หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>10.8</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>46173.9591087963</v>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>46173.98444444445</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0.6081</v>
+      </c>
+      <c r="H20" s="7" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>71-8005 สมัย หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>46159.32643518518</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>46159.35631944444</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.7171999999999999</v>
+      </c>
+      <c r="H21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>71-8005 สมัย หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>8.9</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>46164.92251157408</v>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>46165.30418981481</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>9.160299999999999</v>
+      </c>
+      <c r="H22" s="7" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>71-8005 สมัย หัวลาก10W</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>8.10</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>46165.67719907407</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>46165.96905092592</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>7.0044</v>
+      </c>
+      <c r="H23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>71-8683</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>71-8683 รัฐภูมิ  หัวลาก6W ​ชะอม</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>7.1</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>46153.80390046296</v>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>46153.86599537037</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>1.4903</v>
+      </c>
+      <c r="H24" s="7" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>46152.98504629629</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>46153.00671296296</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>Origin</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>72-1217 เนื้อ หัวลาก10W ตระไคร้</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>46173.69319444444</v>
+      </c>
+      <c r="F26" s="8" t="n">
+        <v>46173.91600694445</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>5.3475</v>
+      </c>
+      <c r="H26" s="7" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H19"/>
+  <autoFilter ref="A4:H26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/03_Unmatched_Legs.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
